--- a/design/地图表.xlsx
+++ b/design/地图表.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="地图|Map" sheetId="1" r:id="Rc6af378ebfb84bf5"/>
     <sheet name="碰撞块|MapSolid" sheetId="2" r:id="Raca5f0d30a7f4fc2"/>
@@ -11,6 +11,10 @@
     <sheet r:id="rId2" name="DEMO规则|Rules" sheetId="7"/>
     <sheet r:id="rId3" name="DEMO初装|Loadout" sheetId="8"/>
     <sheet r:id="rId4" name="场景道具|Scene" sheetId="9"/>
+    <sheet name="遭遇|Encounter" sheetId="10" r:id="rIdCfg10"/>
+    <sheet name="场景交互|SceneAction" sheetId="11" r:id="rIdCfg11"/>
+    <sheet name="炸药桶|Barrel" sheetId="12" r:id="rIdCfg12"/>
+    <sheet name="探索区域|Region" sheetId="13" r:id="rIdCfg13"/>
   </sheets>
 </workbook>
 </file>
@@ -20,12 +24,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="200" formatCode="0"/>
     <numFmt numFmtId="201" formatCode="@"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -70,8 +74,22 @@
       <color rgb="FF20364D"/>
       <name val="Carlito"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF17344A"/>
+      <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Microsoft YaHei"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -123,8 +141,19 @@
         <fgColor rgb="FFBDD3E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CDE1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border/>
     <border>
       <right style="thin">
@@ -216,11 +245,13 @@
         <color rgb="FFE7EFF7"/>
       </top>
     </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -478,6 +509,34 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1231,6 +1290,608 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/cfg10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="101" t="str">
+        <v>遭遇ID</v>
+      </c>
+      <c r="B1" s="101" t="str">
+        <v>地图ID</v>
+      </c>
+      <c r="C1" s="101" t="str">
+        <v>赏金道具ID</v>
+      </c>
+      <c r="D1" s="101" t="str">
+        <v>警戒倍率 基点</v>
+      </c>
+      <c r="E1" s="101" t="str">
+        <v>第二波出生ID |分隔</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="101" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="101" t="str">
+        <v>EncounterIdx</v>
+      </c>
+      <c r="B3" s="101" t="str">
+        <v>MapIdx</v>
+      </c>
+      <c r="C3" s="101" t="str">
+        <v>BountyItemIdx</v>
+      </c>
+      <c r="D3" s="101" t="str">
+        <v>AlertScaleBp</v>
+      </c>
+      <c r="E3" s="101" t="str">
+        <v>SecondWave</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="101" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="101" t="str">
+        <v>交互ID</v>
+      </c>
+      <c r="B1" s="101" t="str">
+        <v>场景ID</v>
+      </c>
+      <c r="C1" s="101" t="str">
+        <v>模式 instant/channel</v>
+      </c>
+      <c r="D1" s="101" t="str">
+        <v>读条时长 Tick</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="101" t="str">
+        <v>string</v>
+      </c>
+      <c r="D2" s="101" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="101" t="str">
+        <v>ActionIdx</v>
+      </c>
+      <c r="B3" s="101" t="str">
+        <v>SceneIdx</v>
+      </c>
+      <c r="C3" s="101" t="str">
+        <v>Mode</v>
+      </c>
+      <c r="D3" s="101" t="str">
+        <v>HoldTicks</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="101" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="101" t="str">
+        <v>炸药桶ID</v>
+      </c>
+      <c r="B1" s="101" t="str">
+        <v>场景ID</v>
+      </c>
+      <c r="C1" s="101" t="str">
+        <v>生命</v>
+      </c>
+      <c r="D1" s="101" t="str">
+        <v>引信时长 Tick</v>
+      </c>
+      <c r="E1" s="101" t="str">
+        <v>爆炸半径 毫米</v>
+      </c>
+      <c r="F1" s="101" t="str">
+        <v>爆炸伤害</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="F2" s="101" t="str">
+        <v>int32</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="101" t="str">
+        <v>BarrelIdx</v>
+      </c>
+      <c r="B3" s="101" t="str">
+        <v>SceneIdx</v>
+      </c>
+      <c r="C3" s="101" t="str">
+        <v>Hp</v>
+      </c>
+      <c r="D3" s="101" t="str">
+        <v>FuseTicks</v>
+      </c>
+      <c r="E3" s="101" t="str">
+        <v>Radius</v>
+      </c>
+      <c r="F3" s="101" t="str">
+        <v>Damage</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="101" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/cfg13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="20" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="101" t="str">
+        <v>区域ID</v>
+      </c>
+      <c r="B1" s="101" t="str">
+        <v>左下X 毫米</v>
+      </c>
+      <c r="C1" s="101" t="str">
+        <v>左下Y 毫米</v>
+      </c>
+      <c r="D1" s="101" t="str">
+        <v>宽度 毫米</v>
+      </c>
+      <c r="E1" s="101" t="str">
+        <v>高度 毫米</v>
+      </c>
+      <c r="F1" s="101" t="str">
+        <v>Boss出生ID |分隔</v>
+      </c>
+      <c r="G1" s="101" t="str">
+        <v>线索场景ID |分隔</v>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="B2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="C2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="D2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="E2" s="101" t="str">
+        <v>int32</v>
+      </c>
+      <c r="F2" s="101" t="str">
+        <v>string</v>
+      </c>
+      <c r="G2" s="101" t="str">
+        <v>string</v>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="101" t="str">
+        <v>RegionIdx</v>
+      </c>
+      <c r="B3" s="101" t="str">
+        <v>X</v>
+      </c>
+      <c r="C3" s="101" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D3" s="101" t="str">
+        <v>W</v>
+      </c>
+      <c r="E3" s="101" t="str">
+        <v>H</v>
+      </c>
+      <c r="F3" s="101" t="str">
+        <v>BossSpawns</v>
+      </c>
+      <c r="G3" s="101" t="str">
+        <v>Clues</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="101" t="str">
+        <v>server/client/key</v>
+      </c>
+      <c r="B4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="C4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="D4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="E4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="F4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+      <c r="G4" s="101" t="str">
+        <v>server/client</v>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="102"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+      <c r="F5" s="102"/>
+      <c r="G5" s="102"/>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="102"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="102"/>
+      <c r="G6" s="102"/>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="102"/>
+      <c r="B7" s="102"/>
+      <c r="C7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="102"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="102"/>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="102"/>
+      <c r="B8" s="102"/>
+      <c r="C8" s="102"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="102"/>
+      <c r="F8" s="102"/>
+      <c r="G8" s="102"/>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="102"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="102"/>
+      <c r="D9" s="102"/>
+      <c r="E9" s="102"/>
+      <c r="F9" s="102"/>
+      <c r="G9" s="102"/>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="102"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="102"/>
+      <c r="B11" s="102"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="102"/>
+      <c r="F11" s="102"/>
+      <c r="G11" s="102"/>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="102"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="102"/>
+      <c r="D12" s="102"/>
+      <c r="E12" s="102"/>
+      <c r="F12" s="102"/>
+      <c r="G12" s="102"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>

--- a/design/地图表.xlsx
+++ b/design/地图表.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="200" formatCode="0"/>
     <numFmt numFmtId="201" formatCode="@"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -87,6 +87,12 @@
     <font>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF20364D"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="14">
@@ -251,7 +257,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="10"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="169">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -537,6 +543,165 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="8" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="8" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="201" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="200" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="7" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="1" fillId="8" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="200" fontId="8" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="201" fontId="8" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="10" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,11 +1535,21 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="A5" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="102" t="n">
+        <v>2800002</v>
+      </c>
+      <c r="D5" s="102" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E5" s="102" t="str">
+        <v>12|13</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="102"/>
@@ -1497,28 +1672,60 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
+      <c r="A5" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="102" t="str">
+        <v>instant</v>
+      </c>
+      <c r="D5" s="102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
+      <c r="A6" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="102" t="str">
+        <v>channel</v>
+      </c>
+      <c r="D6" s="102" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="102"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
+      <c r="A7" s="102" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="102" t="str">
+        <v>channel</v>
+      </c>
+      <c r="D7" s="102" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="102"/>
-      <c r="B8" s="102"/>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
+      <c r="A8" s="102" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" s="102" t="str">
+        <v>channel</v>
+      </c>
+      <c r="D8" s="102" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="A9" s="102"/>
@@ -1642,12 +1849,24 @@
       </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
+      <c r="A5" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="102" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="102" t="n">
+        <v>60</v>
+      </c>
+      <c r="D5" s="102" t="n">
+        <v>60</v>
+      </c>
+      <c r="E5" s="102" t="n">
+        <v>1800</v>
+      </c>
+      <c r="F5" s="102" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
       <c r="A6" s="102"/>
@@ -1721,6 +1940,7 @@
     <col min="5" max="5" width="20" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="20" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="20" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1745,6 +1965,9 @@
       <c r="G1" s="101" t="str">
         <v>线索场景ID |分隔</v>
       </c>
+      <c r="H1" s="168" t="str">
+        <v>所属地图</v>
+      </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="101" t="str">
@@ -1768,6 +1991,9 @@
       <c r="G2" s="101" t="str">
         <v>string</v>
       </c>
+      <c r="H2" s="168" t="str">
+        <v>int32</v>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="101" t="str">
@@ -1791,6 +2017,9 @@
       <c r="G3" s="101" t="str">
         <v>Clues</v>
       </c>
+      <c r="H3" s="168" t="str">
+        <v>MapIdx</v>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="101" t="str">
@@ -1814,24 +2043,61 @@
       <c r="G4" s="101" t="str">
         <v>server/client</v>
       </c>
+      <c r="H4" s="168" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="102"/>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
+      <c r="A5" s="102" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="102" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E5" s="102" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F5" s="102" t="str">
+        <v>15</v>
+      </c>
+      <c r="G5" s="102" t="str">
+        <v>5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" ht="26" customHeight="1">
-      <c r="A6" s="102"/>
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
+      <c r="A6" s="102" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="102" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C6" s="102" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="102" t="n">
+        <v>12000</v>
+      </c>
+      <c r="E6" s="102" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F6" s="102" t="str">
+        <v>14</v>
+      </c>
+      <c r="G6" s="102" t="str">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="102"/>
@@ -10835,7 +11101,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
@@ -10948,8 +11214,8 @@
       <c r="C5" s="88" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="88" t="n">
-        <v>100000001</v>
+      <c r="D5" s="158" t="n">
+        <v>10001</v>
       </c>
       <c r="E5" s="88" t="n">
         <v>2000</v>
@@ -10988,11 +11254,11 @@
       <c r="B7" s="88" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="88" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="88" t="n">
-        <v>100000002</v>
+      <c r="C7" s="158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="158" t="n">
+        <v>10001</v>
       </c>
       <c r="E7" s="88" t="n">
         <v>2000</v>
@@ -15005,12 +15271,12 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
+  <legacyDrawing r:id="rIdField2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr>
     <tabColor rgb="FF577A9A"/>
   </sheetPr>
@@ -15320,8 +15586,8 @@
       <c r="B13" s="88" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="88" t="n">
-        <v>6</v>
+      <c r="C13" s="158" t="n">
+        <v>1002</v>
       </c>
       <c r="D13" s="88" t="n">
         <v>29500</v>
@@ -15343,8 +15609,8 @@
       <c r="B14" s="90" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="90" t="n">
-        <v>7</v>
+      <c r="C14" s="160" t="n">
+        <v>5</v>
       </c>
       <c r="D14" s="90" t="n">
         <v>33500</v>
@@ -15360,13 +15626,27 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="92"/>
-      <c r="B15" s="92"/>
-      <c r="C15" s="92"/>
-      <c r="D15" s="92"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
+      <c r="A15" s="162" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="162" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="162" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D15" s="162" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E15" s="162" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="162" t="n">
+        <v>9600</v>
+      </c>
+      <c r="G15" s="162" t="n">
+        <v>10600</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="92"/>
@@ -19801,7 +20081,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
+  <legacyDrawing r:id="rIdField2"/>
 </worksheet>
 </file>
 
@@ -25263,7 +25543,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
@@ -25272,6 +25552,7 @@
     <col min="4" max="4" width="22" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="22" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="22" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -25293,6 +25574,9 @@
       <c r="F1" s="94" t="str">
         <v>消耗品物品ID序列</v>
       </c>
+      <c r="G1" s="168" t="str">
+        <v>初始技能ID（|分隔，0为无）</v>
+      </c>
     </row>
     <row r="2" ht="32" customHeight="1">
       <c r="A2" s="94" t="str">
@@ -25313,6 +25597,9 @@
       <c r="F2" s="94" t="str">
         <v>string</v>
       </c>
+      <c r="G2" s="168" t="str">
+        <v>string</v>
+      </c>
     </row>
     <row r="3" ht="32" customHeight="1">
       <c r="A3" s="94" t="str">
@@ -25333,6 +25620,9 @@
       <c r="F3" s="94" t="str">
         <v>Consumables</v>
       </c>
+      <c r="G3" s="168" t="str">
+        <v>Skills</v>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="94" t="str">
@@ -25353,6 +25643,9 @@
       <c r="F4" s="94" t="str">
         <v>server/client</v>
       </c>
+      <c r="G4" s="168" t="str">
+        <v>server/client</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1">
       <c r="A5" t="n" s="95">
@@ -25373,15 +25666,18 @@
       <c r="F5" t="str" s="95">
         <v>30004|30006</v>
       </c>
+      <c r="G5" t="str">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
+  <legacyDrawing r:id="rIdField2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22" hidden="0" customWidth="1"/>
@@ -25576,8 +25872,112 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ammo_supply</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4200</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>600</v>
+      </c>
+      <c r="G8" t="n">
+        <v>800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D9" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>400</v>
+      </c>
+      <c r="G9" t="n">
+        <v>600</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>clue</v>
+      </c>
+      <c r="D10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>400</v>
+      </c>
+      <c r="G10" t="n">
+        <v>600</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>barrel</v>
+      </c>
+      <c r="D11" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G11" t="n">
+        <v>800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ns1:id="rIdField2"/>
+  <legacyDrawing r:id="rIdField2"/>
 </worksheet>
 </file>